--- a/Packages/cn.etetet.yiuinumericconfig/Luban/Config/Other/NumericValueAffect.xlsx
+++ b/Packages/cn.etetet.yiuinumericconfig/Luban/Config/Other/NumericValueAffect.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowWidth="21600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -50320,7 +50320,10 @@
       <c r="XEU3"/>
       <c r="XEV3"/>
     </row>
-    <row r="4" ht="116" customHeight="1" spans="2:5">
+    <row r="4" ht="116" customHeight="1" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
@@ -50348,7 +50351,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:5">
+    <row r="6" customHeight="1" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="B6" s="3" t="s">
         <v>18</v>
       </c>
